--- a/crates/xlstream-eval/tests/fixtures/lookup/index_match.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/lookup/index_match.xlsx
@@ -21,15 +21,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
-  <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xmatch</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+  <si>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_pos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xmatch_pos</t>
   </si>
   <si>
     <t xml:space="preserve">index_match</t>
@@ -44,25 +44,10 @@
     <t xml:space="preserve">AMER</t>
   </si>
   <si>
-    <t xml:space="preserve">Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Americas</t>
-  </si>
-  <si>
     <t xml:space="preserve">LATAM</t>
   </si>
   <si>
-    <t xml:space="preserve">LatAm</t>
-  </si>
-  <si>
     <t xml:space="preserve">MEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MidEast</t>
   </si>
 </sst>
 </file>
@@ -335,7 +320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -364,9 +349,9 @@
         <f aca="false">_xlfn.XMATCH(A2,Lookup1!A:A,0)</f>
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="str">
+      <c r="D2" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A2,Lookup1!A:A,0))</f>
-        <v>Europe</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -381,9 +366,9 @@
         <f aca="false">_xlfn.XMATCH(A3,Lookup1!A:A,0)</f>
         <v>2</v>
       </c>
-      <c r="D3" s="0" t="str">
+      <c r="D3" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A3,Lookup1!A:A,0))</f>
-        <v>Asia</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -398,77 +383,77 @@
         <f aca="false">_xlfn.XMATCH(A4,Lookup1!A:A,0)</f>
         <v>3</v>
       </c>
-      <c r="D4" s="0" t="str">
+      <c r="D4" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A4,Lookup1!A:A,0))</f>
-        <v>Americas</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">MATCH(A5,Lookup1!A:A,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" s="0" t="n">
         <f aca="false">_xlfn.XMATCH(A5,Lookup1!A:A,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A5,Lookup1!A:A,0))</f>
-        <v>Europe</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">MATCH(A6,Lookup1!A:A,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">_xlfn.XMATCH(A6,Lookup1!A:A,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D6" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A6,Lookup1!A:A,0))</f>
-        <v>Asia</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">MATCH(A7,Lookup1!A:A,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">_xlfn.XMATCH(A7,Lookup1!A:A,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="str">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A7,Lookup1!A:A,0))</f>
-        <v>Americas</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">MATCH(A8,Lookup1!A:A,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">_xlfn.XMATCH(A8,Lookup1!A:A,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="0" t="str">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A8,Lookup1!A:A,0))</f>
-        <v>Europe</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -483,43 +468,9 @@
         <f aca="false">_xlfn.XMATCH(A9,Lookup1!A:A,0)</f>
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="str">
+      <c r="D9" s="0" t="n">
         <f aca="false">INDEX(Lookup1!B:B,MATCH(A9,Lookup1!A:A,0))</f>
-        <v>Asia</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false">MATCH(A10,Lookup1!A:A,0)</f>
-        <v>3</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(A10,Lookup1!A:A,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D10" s="0" t="str">
-        <f aca="false">INDEX(Lookup1!B:B,MATCH(A10,Lookup1!A:A,0))</f>
-        <v>Americas</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false">MATCH(A11,Lookup1!A:A,0)</f>
-        <v>1</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(A11,Lookup1!A:A,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D11" s="0" t="str">
-        <f aca="false">INDEX(Lookup1!B:B,MATCH(A11,Lookup1!A:A,0))</f>
-        <v>Europe</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -538,17 +489,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="0" t="n">
+      <c r="B1" s="0" t="n">
         <v>100</v>
       </c>
     </row>
@@ -556,10 +504,7 @@
       <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="0" t="n">
         <v>200</v>
       </c>
     </row>
@@ -567,33 +512,24 @@
       <c r="A3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="0" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>75</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
